--- a/artfynd/A 5383-2024 artfynd.xlsx
+++ b/artfynd/A 5383-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5383-2024 artfynd.xlsx
+++ b/artfynd/A 5383-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112119517</v>
+        <v>112119449</v>
       </c>
       <c r="B2" t="n">
-        <v>104383</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>350554</v>
+        <v>350620</v>
       </c>
       <c r="R2" t="n">
-        <v>6426323</v>
+        <v>6426292</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ung planta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112119520</v>
+        <v>112119451</v>
       </c>
       <c r="B3" t="n">
-        <v>104383</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>350592</v>
+        <v>350582</v>
       </c>
       <c r="R3" t="n">
-        <v>6426324</v>
+        <v>6426298</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -858,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ung planta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112119523</v>
+        <v>112119517</v>
       </c>
       <c r="B4" t="n">
-        <v>104383</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350629</v>
+        <v>350554</v>
       </c>
       <c r="R4" t="n">
-        <v>6426313</v>
+        <v>6426323</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ung planta</t>
+          <t>ung planta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,6 +968,312 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112119520</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Länsväg 180 Simmenäsvägen / Vikarydsvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>350592</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6426324</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ung planta</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112119523</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Länsväg 180 Simmenäsvägen / Vikarydsvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>350629</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6426313</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ung planta</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112119526</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Länsväg 180 Simmenäsvägen / Vikarydsvägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>350660</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6426308</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ca 3 meter höga 5 ex</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5383-2024 artfynd.xlsx
+++ b/artfynd/A 5383-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112119449</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112119451</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112119517</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112119520</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112119523</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,8 +1304,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112119526</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>